--- a/outputs/Block2_Historical_Input_Reconciliation_v12.xlsx
+++ b/outputs/Block2_Historical_Input_Reconciliation_v12.xlsx
@@ -73,7 +73,7 @@
     <t>Aggregate loss fields — non-two-party composition exception</t>
   </si>
   <si>
-    <t>Detailed result buckets</t>
+    <t>Final chamber totals — minimum net-transfer reconstruction</t>
   </si>
   <si>
     <t>Resolved</t>
@@ -501,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>233</v>
@@ -548,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>51</v>
@@ -592,10 +592,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>193</v>
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -622,7 +622,7 @@
         <v>20</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -669,7 +669,7 @@
         <v>20</v>
       </c>
       <c r="O5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -686,10 +686,10 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>188</v>
@@ -701,7 +701,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -716,7 +716,7 @@
         <v>20</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -763,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="O7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -780,10 +780,10 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>235</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -827,10 +827,10 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>47</v>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -857,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="O9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -874,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>213</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -904,7 +904,7 @@
         <v>20</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>51</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
